--- a/Performance/trades.xlsx
+++ b/Performance/trades.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Node - v0.18.0</t>
+          <t>Node - v1.0.0</t>
         </is>
       </c>
     </row>
